--- a/DJM01N.xlsx
+++ b/DJM01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="439">
   <si>
     <t/>
   </si>
@@ -305,6 +305,12 @@
   </si>
   <si>
     <t>DJI SAM SOE MAESTR12</t>
+  </si>
+  <si>
+    <t>20139533</t>
+  </si>
+  <si>
+    <t>SMPOERNA PRMA SP 12S</t>
   </si>
   <si>
     <t>10010100</t>
@@ -1714,7 +1720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F209"/>
+  <dimension ref="A1:F210"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2524,7 +2530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>98</v>
       </c>
@@ -2535,13 +2541,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2558,10 +2561,10 @@
         <v>14</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2578,7 +2581,7 @@
         <v>14</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2598,7 +2601,7 @@
         <v>14</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2618,7 +2621,7 @@
         <v>14</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2638,7 +2641,7 @@
         <v>14</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2658,7 +2661,7 @@
         <v>14</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2678,10 +2681,10 @@
         <v>14</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2698,10 +2701,10 @@
         <v>14</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2718,7 +2721,7 @@
         <v>14</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2738,7 +2741,7 @@
         <v>14</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2758,7 +2761,7 @@
         <v>14</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2778,10 +2781,10 @@
         <v>14</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2798,10 +2801,10 @@
         <v>14</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2815,10 +2818,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2838,10 +2841,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2858,10 +2861,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2878,7 +2881,7 @@
         <v>17</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2898,7 +2901,7 @@
         <v>17</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2918,7 +2921,7 @@
         <v>17</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2938,7 +2941,7 @@
         <v>17</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2958,7 +2961,7 @@
         <v>17</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2978,7 +2981,7 @@
         <v>17</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2998,10 +3001,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3018,10 +3021,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3038,7 +3041,7 @@
         <v>17</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3058,7 +3061,7 @@
         <v>17</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3078,7 +3081,7 @@
         <v>17</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3086,19 +3089,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3118,7 +3121,7 @@
         <v>20</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3138,7 +3141,7 @@
         <v>20</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3158,7 +3161,7 @@
         <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3178,7 +3181,7 @@
         <v>20</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3198,7 +3201,7 @@
         <v>20</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3218,7 +3221,7 @@
         <v>20</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3238,7 +3241,7 @@
         <v>20</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3255,10 +3258,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3278,7 +3281,7 @@
         <v>23</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3298,7 +3301,7 @@
         <v>23</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3318,7 +3321,7 @@
         <v>23</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3338,7 +3341,7 @@
         <v>23</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3358,7 +3361,7 @@
         <v>23</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3378,7 +3381,7 @@
         <v>23</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3398,7 +3401,7 @@
         <v>23</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3418,7 +3421,7 @@
         <v>23</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3438,7 +3441,7 @@
         <v>23</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3458,7 +3461,7 @@
         <v>23</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3478,7 +3481,7 @@
         <v>23</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3498,7 +3501,7 @@
         <v>23</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3515,10 +3518,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3538,7 +3541,7 @@
         <v>26</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3558,7 +3561,7 @@
         <v>26</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3578,7 +3581,7 @@
         <v>26</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3598,7 +3601,7 @@
         <v>26</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3618,7 +3621,7 @@
         <v>26</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3638,10 +3641,10 @@
         <v>26</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3658,10 +3661,10 @@
         <v>26</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3678,7 +3681,7 @@
         <v>26</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3698,7 +3701,7 @@
         <v>26</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3715,10 +3718,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3738,7 +3741,7 @@
         <v>29</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3758,7 +3761,7 @@
         <v>29</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3778,7 +3781,7 @@
         <v>29</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3798,7 +3801,7 @@
         <v>29</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3818,7 +3821,7 @@
         <v>29</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3838,7 +3841,7 @@
         <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3858,10 +3861,10 @@
         <v>29</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3878,10 +3881,10 @@
         <v>29</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3895,10 +3898,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3998,7 +4001,7 @@
         <v>33</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4041,7 +4044,7 @@
         <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4061,7 +4064,7 @@
         <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4078,7 +4081,7 @@
         <v>33</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4141,7 +4144,7 @@
         <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4158,10 +4161,10 @@
         <v>33</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4218,7 +4221,7 @@
         <v>33</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4301,7 +4304,7 @@
         <v>17</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4318,10 +4321,10 @@
         <v>33</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4381,7 +4384,7 @@
         <v>20</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4441,7 +4444,7 @@
         <v>20</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4598,10 +4601,10 @@
         <v>33</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4681,7 +4684,7 @@
         <v>23</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4778,7 +4781,7 @@
         <v>33</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4795,10 +4798,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4818,7 +4821,7 @@
         <v>36</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4838,7 +4841,7 @@
         <v>36</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4858,7 +4861,7 @@
         <v>36</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4878,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4898,7 +4901,7 @@
         <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4918,7 +4921,7 @@
         <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4938,7 +4941,7 @@
         <v>36</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4958,7 +4961,7 @@
         <v>36</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4978,7 +4981,7 @@
         <v>36</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4998,7 +5001,7 @@
         <v>36</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5018,10 +5021,10 @@
         <v>36</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5038,10 +5041,10 @@
         <v>36</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5055,10 +5058,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5078,7 +5081,7 @@
         <v>39</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5098,7 +5101,7 @@
         <v>39</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5118,7 +5121,7 @@
         <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5138,7 +5141,7 @@
         <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5158,7 +5161,7 @@
         <v>39</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5178,7 +5181,7 @@
         <v>39</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5198,7 +5201,7 @@
         <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5218,7 +5221,7 @@
         <v>39</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5238,7 +5241,7 @@
         <v>39</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5258,7 +5261,7 @@
         <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5278,7 +5281,7 @@
         <v>39</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5298,7 +5301,7 @@
         <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5315,10 +5318,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5338,7 +5341,7 @@
         <v>42</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5358,7 +5361,7 @@
         <v>42</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5378,7 +5381,7 @@
         <v>42</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5398,7 +5401,7 @@
         <v>42</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5418,10 +5421,10 @@
         <v>42</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5438,10 +5441,10 @@
         <v>42</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5458,7 +5461,7 @@
         <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5478,7 +5481,7 @@
         <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5498,7 +5501,7 @@
         <v>42</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5518,7 +5521,7 @@
         <v>42</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5538,7 +5541,7 @@
         <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5558,7 +5561,7 @@
         <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5578,10 +5581,10 @@
         <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -5598,7 +5601,7 @@
         <v>42</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>30</v>
@@ -5615,13 +5618,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>156</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5638,10 +5641,10 @@
         <v>73</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5658,10 +5661,10 @@
         <v>73</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5678,10 +5681,10 @@
         <v>73</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5698,10 +5701,10 @@
         <v>73</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -5718,10 +5721,10 @@
         <v>73</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5738,10 +5741,10 @@
         <v>73</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5755,13 +5758,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -5775,13 +5778,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -5795,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -5815,13 +5818,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -5835,13 +5838,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -5855,13 +5858,13 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -5875,10 +5878,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5895,13 +5898,33 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E209" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E210" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F209" s="1" t="s">
-        <v>70</v>
+      <c r="F210" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/DJM01N.xlsx
+++ b/DJM01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="429">
   <si>
     <t/>
   </si>
@@ -412,7 +412,7 @@
     <t>20135439</t>
   </si>
   <si>
-    <t>SAMPOERNA 35TH ED16S</t>
+    <t>SAMPOERNA MLD CLS16S</t>
   </si>
   <si>
     <t>20131370</t>
@@ -766,12 +766,6 @@
     <t>TEREA MULINT ED 20'S</t>
   </si>
   <si>
-    <t>20139348</t>
-  </si>
-  <si>
-    <t>TEREA BERMIN PRL 20S</t>
-  </si>
-  <si>
     <t>20140875</t>
   </si>
   <si>
@@ -808,12 +802,6 @@
     <t>TEREA PERINT PRL 20S</t>
   </si>
   <si>
-    <t>20140878</t>
-  </si>
-  <si>
-    <t>BLENDS GOLD 20'S</t>
-  </si>
-  <si>
     <t>20140879</t>
   </si>
   <si>
@@ -994,12 +982,6 @@
     <t>VEEV DVCE KIT SP.GRY</t>
   </si>
   <si>
-    <t>20135716</t>
-  </si>
-  <si>
-    <t>CAMEL SENSO GOLD 20S</t>
-  </si>
-  <si>
     <t>20117925</t>
   </si>
   <si>
@@ -1226,18 +1208,6 @@
   </si>
   <si>
     <t>ESSE DOUBLE POP 16'S</t>
-  </si>
-  <si>
-    <t>20138581</t>
-  </si>
-  <si>
-    <t>ESSE/C CGR CACAO 20S</t>
-  </si>
-  <si>
-    <t>20138582</t>
-  </si>
-  <si>
-    <t>ESSE/C CGR PRPLE 20S</t>
   </si>
   <si>
     <t>20038143</t>
@@ -1720,7 +1690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F210"/>
+  <dimension ref="A1:F205"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4064,7 +4034,7 @@
         <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4081,7 +4051,7 @@
         <v>33</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4144,7 +4114,7 @@
         <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4161,10 +4131,10 @@
         <v>33</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4201,7 +4171,7 @@
         <v>33</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4221,7 +4191,7 @@
         <v>33</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4284,7 +4254,7 @@
         <v>17</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4301,7 +4271,7 @@
         <v>33</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4321,10 +4291,10 @@
         <v>33</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4364,7 +4334,7 @@
         <v>20</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4384,7 +4354,7 @@
         <v>20</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4424,7 +4394,7 @@
         <v>20</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4444,7 +4414,7 @@
         <v>20</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4581,10 +4551,10 @@
         <v>33</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4601,10 +4571,10 @@
         <v>33</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4664,7 +4634,7 @@
         <v>23</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4684,7 +4654,7 @@
         <v>23</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4761,7 +4731,7 @@
         <v>33</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4778,10 +4748,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4798,10 +4768,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4821,7 +4791,7 @@
         <v>36</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4841,7 +4811,7 @@
         <v>36</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4861,7 +4831,7 @@
         <v>36</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4881,7 +4851,7 @@
         <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4901,7 +4871,7 @@
         <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4921,7 +4891,7 @@
         <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4941,7 +4911,7 @@
         <v>36</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4961,7 +4931,7 @@
         <v>36</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4981,10 +4951,10 @@
         <v>36</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5001,7 +4971,7 @@
         <v>36</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5018,10 +4988,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5038,13 +5008,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5058,10 +5028,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5081,7 +5051,7 @@
         <v>39</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5101,7 +5071,7 @@
         <v>39</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5121,7 +5091,7 @@
         <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5141,7 +5111,7 @@
         <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5161,7 +5131,7 @@
         <v>39</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5181,7 +5151,7 @@
         <v>39</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5201,7 +5171,7 @@
         <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5221,7 +5191,7 @@
         <v>39</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5241,7 +5211,7 @@
         <v>39</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5261,7 +5231,7 @@
         <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5278,10 +5248,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5298,10 +5268,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5318,10 +5288,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5341,7 +5311,7 @@
         <v>42</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5361,7 +5331,7 @@
         <v>42</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5381,10 +5351,10 @@
         <v>42</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -5401,7 +5371,7 @@
         <v>42</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5421,7 +5391,7 @@
         <v>42</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5441,10 +5411,10 @@
         <v>42</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5461,7 +5431,7 @@
         <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5481,7 +5451,7 @@
         <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5501,7 +5471,7 @@
         <v>42</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5521,7 +5491,7 @@
         <v>42</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5538,10 +5508,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5558,10 +5528,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5578,10 +5548,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5598,13 +5568,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -5618,13 +5588,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>156</v>
+        <v>17</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5641,7 +5611,7 @@
         <v>73</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5661,7 +5631,7 @@
         <v>73</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5678,10 +5648,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5698,10 +5668,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5718,10 +5688,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5738,10 +5708,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5758,10 +5728,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5781,7 +5751,7 @@
         <v>156</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5801,7 +5771,7 @@
         <v>156</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5821,109 +5791,9 @@
         <v>156</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F206" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F207" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F210" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM01N.xlsx
+++ b/DJM01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="417">
   <si>
     <t/>
   </si>
@@ -31,13 +31,25 @@
     <t>RT</t>
   </si>
   <si>
+    <t>20141502</t>
+  </si>
+  <si>
+    <t>DUNHILL MIXTURES 12S</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
     <t>20055060</t>
   </si>
   <si>
     <t>DUNHILL FC FTLR 16'S</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t>20100889</t>
@@ -46,7 +58,7 @@
     <t>DUNHILL FC FTLR 12'S</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>20002901</t>
@@ -55,7 +67,7 @@
     <t>DUNHILL HIJAU MNTH20</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>20007397</t>
@@ -64,7 +76,7 @@
     <t>DUNHILL BIRU LGHT 20</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t>20096704</t>
@@ -73,7 +85,7 @@
     <t>DUNHILL MILD BKS 16S</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>20039178</t>
@@ -82,7 +94,7 @@
     <t>DUNHILL F/C MILD20'S</t>
   </si>
   <si>
-    <t>7</t>
+    <t>8</t>
   </si>
   <si>
     <t>20137296</t>
@@ -91,21 +103,9 @@
     <t>DUNHILL EVOQUE 16S</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20141502</t>
-  </si>
-  <si>
-    <t>DUNHILL MIXTURES 12S</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
     <t>20137298</t>
   </si>
   <si>
@@ -283,18 +283,6 @@
     <t>SAMPOERNA PRIMA 12'S</t>
   </si>
   <si>
-    <t>20138480</t>
-  </si>
-  <si>
-    <t>SMPOERNA LG NSKA 12S</t>
-  </si>
-  <si>
-    <t>20139347</t>
-  </si>
-  <si>
-    <t>MAGNUM VNTR GLD 12S</t>
-  </si>
-  <si>
     <t>20139534</t>
   </si>
   <si>
@@ -313,6 +301,12 @@
     <t>SMPOERNA PRMA SP 12S</t>
   </si>
   <si>
+    <t>20141927</t>
+  </si>
+  <si>
+    <t>MAGNUM 234 12S</t>
+  </si>
+  <si>
     <t>10010100</t>
   </si>
   <si>
@@ -379,12 +373,6 @@
     <t>DJI SAM SOE MG BIN12</t>
   </si>
   <si>
-    <t>20136297</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE TIN 12S</t>
-  </si>
-  <si>
     <t>10030733</t>
   </si>
   <si>
@@ -445,817 +433,793 @@
     <t>SMPOERNA AVLT MNT 20</t>
   </si>
   <si>
-    <t>20136036</t>
-  </si>
-  <si>
-    <t>SMPOERN AVL TW/BRZ20</t>
-  </si>
-  <si>
     <t>20138598</t>
   </si>
   <si>
     <t>SMPOERN AVL RY.BRS20</t>
   </si>
   <si>
-    <t>20139332</t>
-  </si>
-  <si>
-    <t>MRLBORO SUMMER/B 16S</t>
-  </si>
-  <si>
-    <t>20136035</t>
-  </si>
-  <si>
-    <t>MARLBORO PRPLE BS16S</t>
-  </si>
-  <si>
-    <t>20138112</t>
-  </si>
-  <si>
-    <t>MRLBORO RED TITA.20</t>
-  </si>
-  <si>
-    <t>20138113</t>
-  </si>
-  <si>
-    <t>MRLBORO GOLD TITA.20</t>
+    <t>20033460</t>
+  </si>
+  <si>
+    <t>DJARUM COKLT EXTR12S</t>
+  </si>
+  <si>
+    <t>10010083</t>
+  </si>
+  <si>
+    <t>DJARUM KRT CKT12/PCS</t>
+  </si>
+  <si>
+    <t>20135180</t>
+  </si>
+  <si>
+    <t>DJARUM76 FILT.NNS12S</t>
+  </si>
+  <si>
+    <t>20136122</t>
+  </si>
+  <si>
+    <t>DJRM CKLT EXT MOC 12</t>
+  </si>
+  <si>
+    <t>20130634</t>
+  </si>
+  <si>
+    <t>DJARUM 76 MANGGA 12S</t>
+  </si>
+  <si>
+    <t>20138087</t>
+  </si>
+  <si>
+    <t>DJARUM CKLT ELITE 12</t>
+  </si>
+  <si>
+    <t>20138754</t>
+  </si>
+  <si>
+    <t>DJARUM76 FILT.APL12S</t>
+  </si>
+  <si>
+    <t>20139003</t>
+  </si>
+  <si>
+    <t>DJARUM76 MGA RYL12'S</t>
+  </si>
+  <si>
+    <t>20084820</t>
+  </si>
+  <si>
+    <t>FORTE ORGL BKS 20'S</t>
+  </si>
+  <si>
+    <t>20084821</t>
+  </si>
+  <si>
+    <t>FORTE MNTHL BKS 20'S</t>
+  </si>
+  <si>
+    <t>20132549</t>
+  </si>
+  <si>
+    <t>FORTE MANGO BKS 20'S</t>
+  </si>
+  <si>
+    <t>10014528</t>
+  </si>
+  <si>
+    <t>DJARUM BLACK FILTR16</t>
+  </si>
+  <si>
+    <t>10035030</t>
+  </si>
+  <si>
+    <t>DJRM BLACK CPCINO 16</t>
+  </si>
+  <si>
+    <t>20131992</t>
+  </si>
+  <si>
+    <t>DJARUM MILD F.COLA16</t>
+  </si>
+  <si>
+    <t>20046279</t>
+  </si>
+  <si>
+    <t>DJARUM SPR MILD 20'S</t>
+  </si>
+  <si>
+    <t>20075616</t>
+  </si>
+  <si>
+    <t>DJARUM MILD BLCK 12S</t>
+  </si>
+  <si>
+    <t>10010087</t>
+  </si>
+  <si>
+    <t>MR.BROWN COFFEE 12'S</t>
+  </si>
+  <si>
+    <t>20136123</t>
+  </si>
+  <si>
+    <t>DJARUM ESPRSO GLD12S</t>
+  </si>
+  <si>
+    <t>20132548</t>
+  </si>
+  <si>
+    <t>DJARUM ESPRESSO 12'S</t>
+  </si>
+  <si>
+    <t>20140378</t>
+  </si>
+  <si>
+    <t>DJARUM SUPER WRAP12S</t>
+  </si>
+  <si>
+    <t>20139142</t>
+  </si>
+  <si>
+    <t>DJRM CGRILLOS FC 12S</t>
+  </si>
+  <si>
+    <t>20141969</t>
+  </si>
+  <si>
+    <t>DJRUM 76 APL RYL 12S</t>
+  </si>
+  <si>
+    <t>10010081</t>
+  </si>
+  <si>
+    <t>DJARUM SUPER FILTR12</t>
+  </si>
+  <si>
+    <t>10010082</t>
+  </si>
+  <si>
+    <t>DJARUM SUPER FILTR16</t>
+  </si>
+  <si>
+    <t>20126488</t>
+  </si>
+  <si>
+    <t>DJARUM KING FLTER 12</t>
+  </si>
+  <si>
+    <t>20075632</t>
+  </si>
+  <si>
+    <t>LA BOLD BKS 12'S</t>
+  </si>
+  <si>
+    <t>20062125</t>
+  </si>
+  <si>
+    <t>LA BOLD BKS 20'S</t>
+  </si>
+  <si>
+    <t>20134688</t>
+  </si>
+  <si>
+    <t>LA BOLD BKS NEW 16'S</t>
+  </si>
+  <si>
+    <t>20124037</t>
+  </si>
+  <si>
+    <t>LA ICE FL PR/BST 16S</t>
+  </si>
+  <si>
+    <t>20135993</t>
+  </si>
+  <si>
+    <t>LA ICE MANGO BST 16S</t>
+  </si>
+  <si>
+    <t>20048746</t>
+  </si>
+  <si>
+    <t>LA ICE 16'S BKS</t>
+  </si>
+  <si>
+    <t>10010084</t>
+  </si>
+  <si>
+    <t>LA FILTER LIGHT 16'S</t>
+  </si>
+  <si>
+    <t>20136196</t>
+  </si>
+  <si>
+    <t>CLAS MILD PURPLE 16S</t>
+  </si>
+  <si>
+    <t>10024523</t>
+  </si>
+  <si>
+    <t>CLAS MILD FILTER 16S</t>
+  </si>
+  <si>
+    <t>20137797</t>
+  </si>
+  <si>
+    <t>DPLOMAT EVO MGO 16'S</t>
+  </si>
+  <si>
+    <t>20102167</t>
+  </si>
+  <si>
+    <t>DIPLOMAT EVO16'S</t>
+  </si>
+  <si>
+    <t>20101053</t>
+  </si>
+  <si>
+    <t>JAZY BOLD MILD 20'S</t>
+  </si>
+  <si>
+    <t>20136523</t>
+  </si>
+  <si>
+    <t>JAZY RK POPPIN16'S</t>
+  </si>
+  <si>
+    <t>20095233</t>
+  </si>
+  <si>
+    <t>IDM LGHT CRCKET SLID</t>
+  </si>
+  <si>
+    <t>20123763</t>
+  </si>
+  <si>
+    <t>IDM LGHT TOKAI MOTIF</t>
+  </si>
+  <si>
+    <t>20070579</t>
+  </si>
+  <si>
+    <t>IDM LGHT CRCKT ELKTR</t>
+  </si>
+  <si>
+    <t>20128084</t>
+  </si>
+  <si>
+    <t>TEREA BLUE 20'S</t>
+  </si>
+  <si>
+    <t>20128085</t>
+  </si>
+  <si>
+    <t>TEREA BLCK GRN 20'S</t>
+  </si>
+  <si>
+    <t>20128086</t>
+  </si>
+  <si>
+    <t>TEREA SIENNA 20'S</t>
+  </si>
+  <si>
+    <t>20135433</t>
+  </si>
+  <si>
+    <t>TEREA SUN PEARL 20'S</t>
+  </si>
+  <si>
+    <t>20135434</t>
+  </si>
+  <si>
+    <t>TEREA OASIS PRL 20'S</t>
+  </si>
+  <si>
+    <t>20132739</t>
+  </si>
+  <si>
+    <t>TEREA GOLDEN ED 20'S</t>
+  </si>
+  <si>
+    <t>20134380</t>
+  </si>
+  <si>
+    <t>TEREA MULINT ED 20'S</t>
+  </si>
+  <si>
+    <t>20140875</t>
+  </si>
+  <si>
+    <t>TEREA RIVIERA PR 20S</t>
+  </si>
+  <si>
+    <t>20128089</t>
+  </si>
+  <si>
+    <t>TEREA YUGEN 20'S</t>
+  </si>
+  <si>
+    <t>20134381</t>
+  </si>
+  <si>
+    <t>TEREA AUBURN ED 20'S</t>
+  </si>
+  <si>
+    <t>20134382</t>
+  </si>
+  <si>
+    <t>TEREA BERRNE ED 20'S</t>
+  </si>
+  <si>
+    <t>20138206</t>
+  </si>
+  <si>
+    <t>TEREA BLACK RUBY20S</t>
+  </si>
+  <si>
+    <t>20136323</t>
+  </si>
+  <si>
+    <t>BLENDS WARM.EDT 20'S</t>
+  </si>
+  <si>
+    <t>20136324</t>
+  </si>
+  <si>
+    <t>BLENDS PRPL.EDT 20'S</t>
+  </si>
+  <si>
+    <t>20136325</t>
+  </si>
+  <si>
+    <t>BLENDS BLSM.EDT 20'S</t>
+  </si>
+  <si>
+    <t>20136326</t>
+  </si>
+  <si>
+    <t>BLENDS SMMR.EDT 20'S</t>
+  </si>
+  <si>
+    <t>20138346</t>
+  </si>
+  <si>
+    <t>BLENDS RICH.EDT 20'S</t>
+  </si>
+  <si>
+    <t>20139349</t>
+  </si>
+  <si>
+    <t>TEREA PERINT PRL 20S</t>
+  </si>
+  <si>
+    <t>20140879</t>
+  </si>
+  <si>
+    <t>BLENDS TROPICAL 20'S</t>
+  </si>
+  <si>
+    <t>20135189</t>
+  </si>
+  <si>
+    <t>VEEV ONE1000 STRWBRY</t>
+  </si>
+  <si>
+    <t>20135190</t>
+  </si>
+  <si>
+    <t>VEEV ONE1000 RED.MLN</t>
+  </si>
+  <si>
+    <t>20135191</t>
+  </si>
+  <si>
+    <t>VEEV ONE1000 MANGO</t>
+  </si>
+  <si>
+    <t>20137965</t>
+  </si>
+  <si>
+    <t>VEEV ONE1000 S.APPLE</t>
+  </si>
+  <si>
+    <t>20137967</t>
+  </si>
+  <si>
+    <t>VEEV ONE1000 BLUEBRY</t>
+  </si>
+  <si>
+    <t>20137968</t>
+  </si>
+  <si>
+    <t>VEEV ONE1000 GRAPE</t>
+  </si>
+  <si>
+    <t>20138765</t>
+  </si>
+  <si>
+    <t>VEEV ONE1000 STRW CL</t>
+  </si>
+  <si>
+    <t>20139616</t>
+  </si>
+  <si>
+    <t>VEEV ONE 1000 CHERRY</t>
+  </si>
+  <si>
+    <t>20139759</t>
+  </si>
+  <si>
+    <t>VEEV ONE 500 MANGO</t>
+  </si>
+  <si>
+    <t>20139760</t>
+  </si>
+  <si>
+    <t>VEEV ONE 500 RED MLN</t>
+  </si>
+  <si>
+    <t>20139761</t>
+  </si>
+  <si>
+    <t>VEEV ONE 500 STRW CL</t>
+  </si>
+  <si>
+    <t>20140265</t>
+  </si>
+  <si>
+    <t>VEEV ONE 1000 LT.TEA</t>
+  </si>
+  <si>
+    <t>20140266</t>
+  </si>
+  <si>
+    <t>VEEV ONE 500 LM.TEA</t>
+  </si>
+  <si>
+    <t>20140267</t>
+  </si>
+  <si>
+    <t>VEEV ONE 1000 LM.TEA</t>
+  </si>
+  <si>
+    <t>20137962</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULTRA MNGO</t>
+  </si>
+  <si>
+    <t>20137963</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULTRA GRPE</t>
+  </si>
+  <si>
+    <t>20137964</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULT RED.MLN</t>
+  </si>
+  <si>
+    <t>20138345</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULT SOURPLE</t>
+  </si>
+  <si>
+    <t>20138659</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULTRA STRWB</t>
+  </si>
+  <si>
+    <t>20138763</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULTR STR CL</t>
+  </si>
+  <si>
+    <t>20138764</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULTR PDN CF</t>
+  </si>
+  <si>
+    <t>20139526</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULTRA RSPBR</t>
+  </si>
+  <si>
+    <t>20140252</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULTRA LMN.T</t>
+  </si>
+  <si>
+    <t>20135188</t>
+  </si>
+  <si>
+    <t>VEEV DVCE KIT SP.GRY</t>
+  </si>
+  <si>
+    <t>20117925</t>
+  </si>
+  <si>
+    <t>CAMEL MILD BLUE 16'S</t>
+  </si>
+  <si>
+    <t>20130840</t>
+  </si>
+  <si>
+    <t>CAMEL WHITE NEW 20'S</t>
+  </si>
+  <si>
+    <t>20046794</t>
+  </si>
+  <si>
+    <t>CAMEL WHITE 20'S</t>
+  </si>
+  <si>
+    <t>20115758</t>
+  </si>
+  <si>
+    <t>CAMEL YLOW NEW 20'S</t>
+  </si>
+  <si>
+    <t>20096502</t>
+  </si>
+  <si>
+    <t>CAMEL YELLOW 20'S</t>
+  </si>
+  <si>
+    <t>20060300</t>
+  </si>
+  <si>
+    <t>CAMEL ACT.P MINT 20S</t>
+  </si>
+  <si>
+    <t>20128470</t>
+  </si>
+  <si>
+    <t>CAMEL OPT PURPLE 16S</t>
+  </si>
+  <si>
+    <t>20106190</t>
+  </si>
+  <si>
+    <t>CAMEL OPT PURPLE 12S</t>
+  </si>
+  <si>
+    <t>20114049</t>
+  </si>
+  <si>
+    <t>CAMEL OPT YELLOW 12S</t>
+  </si>
+  <si>
+    <t>20133512</t>
+  </si>
+  <si>
+    <t>CAMEL ACTV MNTHL 20S</t>
+  </si>
+  <si>
+    <t>20138432</t>
+  </si>
+  <si>
+    <t>CAMEL ICE RED 16S</t>
+  </si>
+  <si>
+    <t>20137297</t>
+  </si>
+  <si>
+    <t>CAMEL  KRETEK12'S</t>
+  </si>
+  <si>
+    <t>20130571</t>
+  </si>
+  <si>
+    <t>WIN FILTER CLICK20'S</t>
+  </si>
+  <si>
+    <t>20119629</t>
+  </si>
+  <si>
+    <t>WIN FILTER 20'S</t>
+  </si>
+  <si>
+    <t>20136050</t>
+  </si>
+  <si>
+    <t>WIN KRETEK BERRY 12S</t>
+  </si>
+  <si>
+    <t>20136051</t>
+  </si>
+  <si>
+    <t>WIN KRT NANGKA 12'S</t>
+  </si>
+  <si>
+    <t>20108797</t>
+  </si>
+  <si>
+    <t>WIN BOLD 20'S</t>
+  </si>
+  <si>
+    <t>20135739</t>
+  </si>
+  <si>
+    <t>CLIMAX ICY BKS 20'S</t>
+  </si>
+  <si>
+    <t>20135737</t>
+  </si>
+  <si>
+    <t>CLIMAX MANGO BKS20'S</t>
+  </si>
+  <si>
+    <t>20135736</t>
+  </si>
+  <si>
+    <t>CLIMAX MIX BKS 20'S</t>
+  </si>
+  <si>
+    <t>20112661</t>
+  </si>
+  <si>
+    <t>ESSE PUNCH POP 16'S</t>
+  </si>
+  <si>
+    <t>20070447</t>
+  </si>
+  <si>
+    <t>ESSE BERRY POP 16'S</t>
+  </si>
+  <si>
+    <t>20114735</t>
+  </si>
+  <si>
+    <t>ESSE BERRY POP 12'S</t>
+  </si>
+  <si>
+    <t>20093678</t>
+  </si>
+  <si>
+    <t>ESSE BLUE CHNGE 20'S</t>
+  </si>
+  <si>
+    <t>20010960</t>
+  </si>
+  <si>
+    <t>ESSE FILTER BLUE 20S</t>
+  </si>
+  <si>
+    <t>20138128</t>
+  </si>
+  <si>
+    <t>JUARA  APEL 12S</t>
+  </si>
+  <si>
+    <t>20130786</t>
+  </si>
+  <si>
+    <t>JUARA  MNGGA 12S</t>
+  </si>
+  <si>
+    <t>20095302</t>
+  </si>
+  <si>
+    <t>JUARA  TEH 12S</t>
+  </si>
+  <si>
+    <t>20139245</t>
+  </si>
+  <si>
+    <t>JUARA KRT  BERRY 12S</t>
+  </si>
+  <si>
+    <t>20130785</t>
+  </si>
+  <si>
+    <t>JUARA  JAMBU12S</t>
+  </si>
+  <si>
+    <t>20141660</t>
+  </si>
+  <si>
+    <t>JUARA KRT PISANG 12S</t>
+  </si>
+  <si>
+    <t>20085760</t>
+  </si>
+  <si>
+    <t>ESSE CHANGE GRP 20'S</t>
+  </si>
+  <si>
+    <t>20112781</t>
+  </si>
+  <si>
+    <t>ESSE CHNG JUICY 16'S</t>
+  </si>
+  <si>
+    <t>20094203</t>
+  </si>
+  <si>
+    <t>ESSE CHNG JUICY 20'S</t>
+  </si>
+  <si>
+    <t>20112785</t>
+  </si>
+  <si>
+    <t>ESSE CHNG APLMNT 16S</t>
+  </si>
+  <si>
+    <t>20055795</t>
+  </si>
+  <si>
+    <t>ESSE CHNG APLMNT 20S</t>
+  </si>
+  <si>
+    <t>20100795</t>
+  </si>
+  <si>
+    <t>ESSE CHNG DOUB 20'S</t>
+  </si>
+  <si>
+    <t>20126307</t>
+  </si>
+  <si>
+    <t>ESSE DOUBLE POP 16'S</t>
+  </si>
+  <si>
+    <t>20038143</t>
+  </si>
+  <si>
+    <t>GG SURYA EXCLSIVE16S</t>
+  </si>
+  <si>
+    <t>10010077</t>
+  </si>
+  <si>
+    <t>GG SURYA PRO 16'S</t>
+  </si>
+  <si>
+    <t>20054562</t>
+  </si>
+  <si>
+    <t>GG MILD SHIVER 16'S</t>
+  </si>
+  <si>
+    <t>20029731</t>
+  </si>
+  <si>
+    <t>GG SURYA PRO MLD16'S</t>
+  </si>
+  <si>
+    <t>20048021</t>
+  </si>
+  <si>
+    <t>G/G  SGNTURE 12</t>
+  </si>
+  <si>
+    <t>20098634</t>
+  </si>
+  <si>
+    <t>GG KRTEK PATRA 12'S</t>
+  </si>
+  <si>
+    <t>20069791</t>
+  </si>
+  <si>
+    <t>GG SIGNT MILD 16'S</t>
+  </si>
+  <si>
+    <t>10010078</t>
+  </si>
+  <si>
+    <t>GG FILTER MERAH 12'S</t>
   </si>
   <si>
     <t>15</t>
-  </si>
-  <si>
-    <t>20033460</t>
-  </si>
-  <si>
-    <t>DJARUM COKLT EXTR12S</t>
-  </si>
-  <si>
-    <t>10010083</t>
-  </si>
-  <si>
-    <t>DJARUM KRT CKT12/PCS</t>
-  </si>
-  <si>
-    <t>20135180</t>
-  </si>
-  <si>
-    <t>DJARUM76 FILT.NNS12S</t>
-  </si>
-  <si>
-    <t>20136122</t>
-  </si>
-  <si>
-    <t>DJRM CKLT EXT MOC 12</t>
-  </si>
-  <si>
-    <t>20130634</t>
-  </si>
-  <si>
-    <t>DJARUM 76 MANGGA 12S</t>
-  </si>
-  <si>
-    <t>20138087</t>
-  </si>
-  <si>
-    <t>DJARUM CKLT ELITE 12</t>
-  </si>
-  <si>
-    <t>20138754</t>
-  </si>
-  <si>
-    <t>DJARUM76 FILT.APL12S</t>
-  </si>
-  <si>
-    <t>20139003</t>
-  </si>
-  <si>
-    <t>DJARUM76 MGA RYL12'S</t>
-  </si>
-  <si>
-    <t>20084820</t>
-  </si>
-  <si>
-    <t>FORTE ORGL BKS 20'S</t>
-  </si>
-  <si>
-    <t>20084821</t>
-  </si>
-  <si>
-    <t>FORTE MNTHL BKS 20'S</t>
-  </si>
-  <si>
-    <t>20132549</t>
-  </si>
-  <si>
-    <t>FORTE MANGO BKS 20'S</t>
-  </si>
-  <si>
-    <t>10014528</t>
-  </si>
-  <si>
-    <t>DJARUM BLACK FILTR16</t>
-  </si>
-  <si>
-    <t>10035030</t>
-  </si>
-  <si>
-    <t>DJRM BLACK CPCINO 16</t>
-  </si>
-  <si>
-    <t>20131992</t>
-  </si>
-  <si>
-    <t>DJARUM MILD F.COLA16</t>
-  </si>
-  <si>
-    <t>20046279</t>
-  </si>
-  <si>
-    <t>DJARUM SPR MILD 20'S</t>
-  </si>
-  <si>
-    <t>20075616</t>
-  </si>
-  <si>
-    <t>DJARUM MILD BLCK 12S</t>
-  </si>
-  <si>
-    <t>10010087</t>
-  </si>
-  <si>
-    <t>MR.BROWN COFFEE 12'S</t>
-  </si>
-  <si>
-    <t>20136123</t>
-  </si>
-  <si>
-    <t>DJARUM ESPRSO GLD12S</t>
-  </si>
-  <si>
-    <t>20132548</t>
-  </si>
-  <si>
-    <t>DJARUM ESPRESSO 12'S</t>
-  </si>
-  <si>
-    <t>20140378</t>
-  </si>
-  <si>
-    <t>DJARUM SUPER WRAP12S</t>
-  </si>
-  <si>
-    <t>20139142</t>
-  </si>
-  <si>
-    <t>DJRM CGRILLOS FC 12S</t>
-  </si>
-  <si>
-    <t>10010081</t>
-  </si>
-  <si>
-    <t>DJARUM SUPER FILTR12</t>
-  </si>
-  <si>
-    <t>10010082</t>
-  </si>
-  <si>
-    <t>DJARUM SUPER FILTR16</t>
-  </si>
-  <si>
-    <t>20126488</t>
-  </si>
-  <si>
-    <t>DJARUM KING FLTER 12</t>
-  </si>
-  <si>
-    <t>20075632</t>
-  </si>
-  <si>
-    <t>LA BOLD BKS 12'S</t>
-  </si>
-  <si>
-    <t>20062125</t>
-  </si>
-  <si>
-    <t>LA BOLD BKS 20'S</t>
-  </si>
-  <si>
-    <t>20134688</t>
-  </si>
-  <si>
-    <t>LA BOLD BKS NEW 16'S</t>
-  </si>
-  <si>
-    <t>20124037</t>
-  </si>
-  <si>
-    <t>LA ICE FL PR/BST 16S</t>
-  </si>
-  <si>
-    <t>20135993</t>
-  </si>
-  <si>
-    <t>LA ICE MANGO BST 16S</t>
-  </si>
-  <si>
-    <t>20048746</t>
-  </si>
-  <si>
-    <t>LA ICE 16'S BKS</t>
-  </si>
-  <si>
-    <t>10010084</t>
-  </si>
-  <si>
-    <t>LA FILTER LIGHT 16'S</t>
-  </si>
-  <si>
-    <t>20136196</t>
-  </si>
-  <si>
-    <t>CLAS MILD PURPLE 16S</t>
-  </si>
-  <si>
-    <t>10024523</t>
-  </si>
-  <si>
-    <t>CLAS MILD FILTER 16S</t>
-  </si>
-  <si>
-    <t>20137797</t>
-  </si>
-  <si>
-    <t>DPLOMAT EVO MGO 16'S</t>
-  </si>
-  <si>
-    <t>20102167</t>
-  </si>
-  <si>
-    <t>DIPLOMAT EVO16'S</t>
-  </si>
-  <si>
-    <t>20101053</t>
-  </si>
-  <si>
-    <t>JAZY BOLD MILD 20'S</t>
-  </si>
-  <si>
-    <t>20136523</t>
-  </si>
-  <si>
-    <t>JAZY RK POPPIN16'S</t>
-  </si>
-  <si>
-    <t>20095233</t>
-  </si>
-  <si>
-    <t>IDM LGHT CRCKET SLID</t>
-  </si>
-  <si>
-    <t>20123763</t>
-  </si>
-  <si>
-    <t>IDM LGHT TOKAI MOTIF</t>
-  </si>
-  <si>
-    <t>20070579</t>
-  </si>
-  <si>
-    <t>IDM LGHT CRCKT ELKTR</t>
-  </si>
-  <si>
-    <t>20128084</t>
-  </si>
-  <si>
-    <t>TEREA BLUE 20'S</t>
-  </si>
-  <si>
-    <t>20128085</t>
-  </si>
-  <si>
-    <t>TEREA BLCK GRN 20'S</t>
-  </si>
-  <si>
-    <t>20128086</t>
-  </si>
-  <si>
-    <t>TEREA SIENNA 20'S</t>
-  </si>
-  <si>
-    <t>20135433</t>
-  </si>
-  <si>
-    <t>TEREA SUN PEARL 20'S</t>
-  </si>
-  <si>
-    <t>20135434</t>
-  </si>
-  <si>
-    <t>TEREA OASIS PRL 20'S</t>
-  </si>
-  <si>
-    <t>20132739</t>
-  </si>
-  <si>
-    <t>TEREA GOLDEN ED 20'S</t>
-  </si>
-  <si>
-    <t>20134380</t>
-  </si>
-  <si>
-    <t>TEREA MULINT ED 20'S</t>
-  </si>
-  <si>
-    <t>20140875</t>
-  </si>
-  <si>
-    <t>TEREA RIVIERA PR 20S</t>
-  </si>
-  <si>
-    <t>20128089</t>
-  </si>
-  <si>
-    <t>TEREA YUGEN 20'S</t>
-  </si>
-  <si>
-    <t>20134381</t>
-  </si>
-  <si>
-    <t>TEREA AUBURN ED 20'S</t>
-  </si>
-  <si>
-    <t>20134382</t>
-  </si>
-  <si>
-    <t>TEREA BERRNE ED 20'S</t>
-  </si>
-  <si>
-    <t>20138206</t>
-  </si>
-  <si>
-    <t>TEREA BLACK RUBY20S</t>
-  </si>
-  <si>
-    <t>20139349</t>
-  </si>
-  <si>
-    <t>TEREA PERINT PRL 20S</t>
-  </si>
-  <si>
-    <t>20140879</t>
-  </si>
-  <si>
-    <t>BLENDS TROPICAL 20'S</t>
-  </si>
-  <si>
-    <t>20136323</t>
-  </si>
-  <si>
-    <t>BLENDS WARM.EDT 20'S</t>
-  </si>
-  <si>
-    <t>20136324</t>
-  </si>
-  <si>
-    <t>BLENDS PRPL.EDT 20'S</t>
-  </si>
-  <si>
-    <t>20136325</t>
-  </si>
-  <si>
-    <t>BLENDS BLSM.EDT 20'S</t>
-  </si>
-  <si>
-    <t>20136326</t>
-  </si>
-  <si>
-    <t>BLENDS SMMR.EDT 20'S</t>
-  </si>
-  <si>
-    <t>20138346</t>
-  </si>
-  <si>
-    <t>BLENDS RICH.EDT 20'S</t>
-  </si>
-  <si>
-    <t>20135189</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 STRWBRY</t>
-  </si>
-  <si>
-    <t>20135190</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 RED.MLN</t>
-  </si>
-  <si>
-    <t>20135191</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 MANGO</t>
-  </si>
-  <si>
-    <t>20137965</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 S.APPLE</t>
-  </si>
-  <si>
-    <t>20137967</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 BLUEBRY</t>
-  </si>
-  <si>
-    <t>20137968</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 GRAPE</t>
-  </si>
-  <si>
-    <t>20138765</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 STRW CL</t>
-  </si>
-  <si>
-    <t>20139616</t>
-  </si>
-  <si>
-    <t>VEEV ONE 1000 CHERRY</t>
-  </si>
-  <si>
-    <t>20139759</t>
-  </si>
-  <si>
-    <t>VEEV ONE 500 MANGO</t>
-  </si>
-  <si>
-    <t>20139760</t>
-  </si>
-  <si>
-    <t>VEEV ONE 500 RED MLN</t>
-  </si>
-  <si>
-    <t>20139761</t>
-  </si>
-  <si>
-    <t>VEEV ONE 500 STRW CL</t>
-  </si>
-  <si>
-    <t>20140265</t>
-  </si>
-  <si>
-    <t>VEEV ONE 1000 LT.TEA</t>
-  </si>
-  <si>
-    <t>20140266</t>
-  </si>
-  <si>
-    <t>VEEV ONE 500 LM.TEA</t>
-  </si>
-  <si>
-    <t>20140267</t>
-  </si>
-  <si>
-    <t>VEEV ONE 1000 LM.TEA</t>
-  </si>
-  <si>
-    <t>20137962</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTRA MNGO</t>
-  </si>
-  <si>
-    <t>20137963</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTRA GRPE</t>
-  </si>
-  <si>
-    <t>20137964</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULT RED.MLN</t>
-  </si>
-  <si>
-    <t>20138345</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULT SOURPLE</t>
-  </si>
-  <si>
-    <t>20138659</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTRA STRWB</t>
-  </si>
-  <si>
-    <t>20138763</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTR STR CL</t>
-  </si>
-  <si>
-    <t>20138764</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTR PDN CF</t>
-  </si>
-  <si>
-    <t>20139526</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTRA RSPBR</t>
-  </si>
-  <si>
-    <t>20140252</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTRA LMN.T</t>
-  </si>
-  <si>
-    <t>20135188</t>
-  </si>
-  <si>
-    <t>VEEV DVCE KIT SP.GRY</t>
-  </si>
-  <si>
-    <t>20117925</t>
-  </si>
-  <si>
-    <t>CAMEL MILD BLUE 16'S</t>
-  </si>
-  <si>
-    <t>20130840</t>
-  </si>
-  <si>
-    <t>CAMEL WHITE NEW 20'S</t>
-  </si>
-  <si>
-    <t>20046794</t>
-  </si>
-  <si>
-    <t>CAMEL WHITE 20'S</t>
-  </si>
-  <si>
-    <t>20115758</t>
-  </si>
-  <si>
-    <t>CAMEL YLOW NEW 20'S</t>
-  </si>
-  <si>
-    <t>20096502</t>
-  </si>
-  <si>
-    <t>CAMEL YELLOW 20'S</t>
-  </si>
-  <si>
-    <t>20060300</t>
-  </si>
-  <si>
-    <t>CAMEL ACT.P MINT 20S</t>
-  </si>
-  <si>
-    <t>20128470</t>
-  </si>
-  <si>
-    <t>CAMEL OPT PURPLE 16S</t>
-  </si>
-  <si>
-    <t>20106190</t>
-  </si>
-  <si>
-    <t>CAMEL OPT PURPLE 12S</t>
-  </si>
-  <si>
-    <t>20114049</t>
-  </si>
-  <si>
-    <t>CAMEL OPT YELLOW 12S</t>
-  </si>
-  <si>
-    <t>20133512</t>
-  </si>
-  <si>
-    <t>CAMEL ACTV MNTHL 20S</t>
-  </si>
-  <si>
-    <t>20138432</t>
-  </si>
-  <si>
-    <t>CAMEL ICE RED 16S</t>
-  </si>
-  <si>
-    <t>20137297</t>
-  </si>
-  <si>
-    <t>CAMEL  KRETEK12'S</t>
-  </si>
-  <si>
-    <t>20130571</t>
-  </si>
-  <si>
-    <t>WIN FILTER CLICK20'S</t>
-  </si>
-  <si>
-    <t>20119629</t>
-  </si>
-  <si>
-    <t>WIN FILTER 20'S</t>
-  </si>
-  <si>
-    <t>20136050</t>
-  </si>
-  <si>
-    <t>WIN KRETEK BERRY 12S</t>
-  </si>
-  <si>
-    <t>20136051</t>
-  </si>
-  <si>
-    <t>WIN KRT NANGKA 12'S</t>
-  </si>
-  <si>
-    <t>20108797</t>
-  </si>
-  <si>
-    <t>WIN BOLD 20'S</t>
-  </si>
-  <si>
-    <t>20135739</t>
-  </si>
-  <si>
-    <t>CLIMAX ICY BKS 20'S</t>
-  </si>
-  <si>
-    <t>20135737</t>
-  </si>
-  <si>
-    <t>CLIMAX MANGO BKS20'S</t>
-  </si>
-  <si>
-    <t>20135736</t>
-  </si>
-  <si>
-    <t>CLIMAX MIX BKS 20'S</t>
-  </si>
-  <si>
-    <t>20112661</t>
-  </si>
-  <si>
-    <t>ESSE PUNCH POP 16'S</t>
-  </si>
-  <si>
-    <t>20070447</t>
-  </si>
-  <si>
-    <t>ESSE BERRY POP 16'S</t>
-  </si>
-  <si>
-    <t>20114735</t>
-  </si>
-  <si>
-    <t>ESSE BERRY POP 12'S</t>
-  </si>
-  <si>
-    <t>20093678</t>
-  </si>
-  <si>
-    <t>ESSE BLUE CHNGE 20'S</t>
-  </si>
-  <si>
-    <t>20010960</t>
-  </si>
-  <si>
-    <t>ESSE FILTER BLUE 20S</t>
-  </si>
-  <si>
-    <t>20138128</t>
-  </si>
-  <si>
-    <t>JUARA  APEL 12S</t>
-  </si>
-  <si>
-    <t>20130786</t>
-  </si>
-  <si>
-    <t>JUARA  MNGGA 12S</t>
-  </si>
-  <si>
-    <t>20095302</t>
-  </si>
-  <si>
-    <t>JUARA  TEH 12S</t>
-  </si>
-  <si>
-    <t>20139245</t>
-  </si>
-  <si>
-    <t>JUARA KRT  BERRY 12S</t>
-  </si>
-  <si>
-    <t>20130785</t>
-  </si>
-  <si>
-    <t>JUARA  JAMBU12S</t>
-  </si>
-  <si>
-    <t>20141660</t>
-  </si>
-  <si>
-    <t>JUARA KRT PISANG 12S</t>
-  </si>
-  <si>
-    <t>20085760</t>
-  </si>
-  <si>
-    <t>ESSE CHANGE GRP 20'S</t>
-  </si>
-  <si>
-    <t>20112781</t>
-  </si>
-  <si>
-    <t>ESSE CHNG JUICY 16'S</t>
-  </si>
-  <si>
-    <t>20094203</t>
-  </si>
-  <si>
-    <t>ESSE CHNG JUICY 20'S</t>
-  </si>
-  <si>
-    <t>20112785</t>
-  </si>
-  <si>
-    <t>ESSE CHNG APLMNT 16S</t>
-  </si>
-  <si>
-    <t>20055795</t>
-  </si>
-  <si>
-    <t>ESSE CHNG APLMNT 20S</t>
-  </si>
-  <si>
-    <t>20100795</t>
-  </si>
-  <si>
-    <t>ESSE CHNG DOUB 20'S</t>
-  </si>
-  <si>
-    <t>20126307</t>
-  </si>
-  <si>
-    <t>ESSE DOUBLE POP 16'S</t>
-  </si>
-  <si>
-    <t>20038143</t>
-  </si>
-  <si>
-    <t>GG SURYA EXCLSIVE16S</t>
-  </si>
-  <si>
-    <t>10010077</t>
-  </si>
-  <si>
-    <t>GG SURYA PRO 16'S</t>
-  </si>
-  <si>
-    <t>20054562</t>
-  </si>
-  <si>
-    <t>GG MILD SHIVER 16'S</t>
-  </si>
-  <si>
-    <t>20029731</t>
-  </si>
-  <si>
-    <t>GG SURYA PRO MLD16'S</t>
-  </si>
-  <si>
-    <t>20048021</t>
-  </si>
-  <si>
-    <t>G/G  SGNTURE 12</t>
-  </si>
-  <si>
-    <t>20098634</t>
-  </si>
-  <si>
-    <t>GG KRTEK PATRA 12'S</t>
-  </si>
-  <si>
-    <t>20069791</t>
-  </si>
-  <si>
-    <t>GG SIGNT MILD 16'S</t>
-  </si>
-  <si>
-    <t>10010078</t>
-  </si>
-  <si>
-    <t>GG FILTER MERAH 12'S</t>
   </si>
   <si>
     <t>10010075</t>
@@ -1690,7 +1654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F205"/>
+  <dimension ref="A1:F199"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1757,15 +1721,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -1774,7 +1738,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -1782,10 +1746,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -1794,7 +1758,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -1802,10 +1766,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -1814,7 +1778,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -1822,10 +1786,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -1834,7 +1798,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -1842,10 +1806,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -1854,7 +1818,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -1862,10 +1826,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -1874,7 +1838,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -1882,10 +1846,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1894,10 +1858,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2034,7 +1998,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>49</v>
@@ -2054,7 +2018,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>49</v>
@@ -2074,7 +2038,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>49</v>
@@ -2094,7 +2058,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -2114,7 +2078,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -2134,7 +2098,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -2154,7 +2118,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -2271,7 +2235,7 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>4</v>
@@ -2291,7 +2255,7 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>8</v>
@@ -2311,10 +2275,10 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>70</v>
@@ -2331,10 +2295,10 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2351,10 +2315,10 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2371,13 +2335,13 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2391,10 +2355,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2411,10 +2375,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2431,13 +2395,13 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2451,10 +2415,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2471,10 +2435,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2491,16 +2455,16 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>98</v>
       </c>
@@ -2511,10 +2475,13 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2528,13 +2495,13 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2548,10 +2515,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2568,10 +2535,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2588,10 +2555,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2608,10 +2575,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2628,10 +2595,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2648,13 +2615,13 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2668,13 +2635,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2688,10 +2655,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2708,10 +2675,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2728,13 +2695,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2748,10 +2715,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2768,13 +2735,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2788,13 +2755,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2808,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2828,13 +2795,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2848,10 +2815,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2868,10 +2835,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2888,10 +2855,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2908,10 +2875,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2928,13 +2895,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2948,10 +2915,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2968,10 +2935,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2988,13 +2955,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3008,10 +2975,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3028,10 +2995,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3048,10 +3015,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3068,10 +3035,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3079,19 +3046,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3099,19 +3066,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3119,19 +3086,19 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3139,19 +3106,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3159,19 +3126,19 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3179,19 +3146,19 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3199,19 +3166,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3219,19 +3186,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3239,19 +3206,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3259,19 +3226,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3279,19 +3246,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3299,19 +3266,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3319,19 +3286,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3339,19 +3306,19 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3359,19 +3326,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3379,19 +3346,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3399,19 +3366,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3419,19 +3386,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3439,19 +3406,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3459,19 +3426,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3479,19 +3446,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3499,39 +3466,39 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3539,19 +3506,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3559,19 +3526,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3579,19 +3546,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3599,19 +3566,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3619,39 +3586,39 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3659,19 +3626,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3679,19 +3646,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3699,19 +3666,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3719,39 +3686,39 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3759,19 +3726,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3779,19 +3746,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3799,19 +3766,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3819,19 +3786,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3839,39 +3806,39 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3879,10 +3846,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3891,7 +3858,7 @@
         <v>33</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3899,10 +3866,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3911,7 +3878,7 @@
         <v>33</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3919,10 +3886,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3931,7 +3898,7 @@
         <v>33</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3939,10 +3906,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>244</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3951,7 +3918,7 @@
         <v>33</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3959,10 +3926,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3971,7 +3938,7 @@
         <v>33</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3979,10 +3946,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3991,18 +3958,18 @@
         <v>33</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>250</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -4011,7 +3978,7 @@
         <v>33</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4019,10 +3986,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -4031,7 +3998,7 @@
         <v>33</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -4039,10 +4006,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>254</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -4051,7 +4018,7 @@
         <v>33</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4059,10 +4026,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -4071,7 +4038,7 @@
         <v>33</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4079,10 +4046,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4091,18 +4058,18 @@
         <v>33</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>260</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4111,18 +4078,18 @@
         <v>33</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4131,7 +4098,7 @@
         <v>33</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4139,10 +4106,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -4151,7 +4118,7 @@
         <v>33</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4159,10 +4126,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4171,7 +4138,7 @@
         <v>33</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4179,10 +4146,10 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4191,7 +4158,7 @@
         <v>33</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4199,10 +4166,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4211,18 +4178,18 @@
         <v>33</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -4231,18 +4198,18 @@
         <v>33</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>274</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -4251,18 +4218,18 @@
         <v>33</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>276</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4271,7 +4238,7 @@
         <v>33</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4279,10 +4246,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4291,7 +4258,7 @@
         <v>33</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4299,10 +4266,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4311,7 +4278,7 @@
         <v>33</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4319,10 +4286,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4331,18 +4298,18 @@
         <v>33</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>284</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4351,18 +4318,18 @@
         <v>33</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4371,18 +4338,18 @@
         <v>33</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4391,7 +4358,7 @@
         <v>33</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4399,10 +4366,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4411,7 +4378,7 @@
         <v>33</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4419,10 +4386,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4431,18 +4398,18 @@
         <v>33</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4451,18 +4418,18 @@
         <v>33</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -4471,18 +4438,18 @@
         <v>33</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
@@ -4491,18 +4458,18 @@
         <v>33</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
@@ -4511,7 +4478,7 @@
         <v>33</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4519,10 +4486,10 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>302</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
@@ -4531,7 +4498,7 @@
         <v>33</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4539,10 +4506,10 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>304</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
@@ -4551,18 +4518,18 @@
         <v>33</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
@@ -4571,18 +4538,18 @@
         <v>33</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>308</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
@@ -4591,18 +4558,18 @@
         <v>33</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
@@ -4611,27 +4578,27 @@
         <v>33</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4639,19 +4606,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4659,19 +4626,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4679,19 +4646,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4699,19 +4666,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4719,19 +4686,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4739,10 +4706,10 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>324</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
@@ -4751,7 +4718,7 @@
         <v>36</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4759,10 +4726,10 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
@@ -4771,7 +4738,7 @@
         <v>36</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4779,10 +4746,10 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
@@ -4791,7 +4758,7 @@
         <v>36</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4799,10 +4766,10 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>330</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
@@ -4811,7 +4778,7 @@
         <v>36</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4819,10 +4786,10 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
@@ -4831,18 +4798,18 @@
         <v>36</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
@@ -4851,7 +4818,7 @@
         <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4859,19 +4826,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4879,19 +4846,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4899,19 +4866,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4919,19 +4886,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4939,39 +4906,39 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4979,10 +4946,10 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
@@ -4991,7 +4958,7 @@
         <v>39</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -4999,10 +4966,10 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
@@ -5011,7 +4978,7 @@
         <v>39</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5019,10 +4986,10 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
@@ -5031,7 +4998,7 @@
         <v>39</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5039,10 +5006,10 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
@@ -5051,7 +5018,7 @@
         <v>39</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5059,10 +5026,10 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
@@ -5071,7 +5038,7 @@
         <v>39</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5079,10 +5046,10 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
@@ -5091,7 +5058,7 @@
         <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5099,10 +5066,10 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>360</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
@@ -5111,7 +5078,7 @@
         <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5119,19 +5086,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5139,19 +5106,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5159,19 +5126,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5179,19 +5146,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5199,19 +5166,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5219,30 +5186,30 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>374</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
@@ -5251,7 +5218,7 @@
         <v>42</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5259,10 +5226,10 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>376</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
@@ -5271,7 +5238,7 @@
         <v>42</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5279,10 +5246,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
@@ -5291,7 +5258,7 @@
         <v>42</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5299,10 +5266,10 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
@@ -5311,7 +5278,7 @@
         <v>42</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5319,10 +5286,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
@@ -5331,7 +5298,7 @@
         <v>42</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5339,10 +5306,10 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
@@ -5351,18 +5318,18 @@
         <v>42</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>386</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
@@ -5371,7 +5338,7 @@
         <v>42</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5379,19 +5346,19 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5399,19 +5366,19 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5419,19 +5386,19 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5439,19 +5406,19 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5459,19 +5426,19 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5479,19 +5446,19 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5499,10 +5466,10 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
@@ -5511,7 +5478,7 @@
         <v>73</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5519,19 +5486,19 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="E192" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5548,10 +5515,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>73</v>
+        <v>402</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5568,10 +5535,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>73</v>
+        <v>402</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5588,10 +5555,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>73</v>
+        <v>402</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5608,10 +5575,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>73</v>
+        <v>402</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5628,10 +5595,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>73</v>
+        <v>402</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5648,10 +5615,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>156</v>
+        <v>402</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5668,132 +5635,12 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>156</v>
+        <v>402</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F200" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F201" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F202" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F203" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F204" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F205" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM01N.xlsx
+++ b/DJM01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="423">
   <si>
     <t/>
   </si>
@@ -1015,6 +1015,12 @@
     <t>CAMEL  KRETEK12'S</t>
   </si>
   <si>
+    <t>20142259</t>
+  </si>
+  <si>
+    <t>CAMEL ICE LIME 16S</t>
+  </si>
+  <si>
     <t>20130571</t>
   </si>
   <si>
@@ -1129,6 +1135,18 @@
     <t>JUARA KRT PISANG 12S</t>
   </si>
   <si>
+    <t>20142217</t>
+  </si>
+  <si>
+    <t>JUARA KLIK GRN GRP12</t>
+  </si>
+  <si>
+    <t>20142218</t>
+  </si>
+  <si>
+    <t>JUARA KLIK BERRY 12S</t>
+  </si>
+  <si>
     <t>20085760</t>
   </si>
   <si>
@@ -1171,6 +1189,9 @@
     <t>ESSE DOUBLE POP 16'S</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>20038143</t>
   </si>
   <si>
@@ -1217,9 +1238,6 @@
   </si>
   <si>
     <t>GG FILTER MERAH 12'S</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>10010075</t>
@@ -1654,7 +1672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F199"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4835,13 +4853,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4858,7 +4876,7 @@
         <v>39</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4878,7 +4896,7 @@
         <v>39</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4898,7 +4916,7 @@
         <v>39</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4918,7 +4936,7 @@
         <v>39</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4938,7 +4956,7 @@
         <v>39</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4958,7 +4976,7 @@
         <v>39</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -4978,7 +4996,7 @@
         <v>39</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -4998,7 +5016,7 @@
         <v>39</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5018,7 +5036,7 @@
         <v>39</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5038,7 +5056,7 @@
         <v>39</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5058,7 +5076,7 @@
         <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5078,7 +5096,7 @@
         <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5095,10 +5113,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E172" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5118,7 +5136,7 @@
         <v>42</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5138,7 +5156,7 @@
         <v>42</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5158,7 +5176,7 @@
         <v>42</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5178,7 +5196,7 @@
         <v>42</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5198,10 +5216,10 @@
         <v>42</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5218,10 +5236,10 @@
         <v>42</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5238,10 +5256,10 @@
         <v>42</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5258,10 +5276,10 @@
         <v>42</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5278,7 +5296,7 @@
         <v>42</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5298,7 +5316,7 @@
         <v>42</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5318,7 +5336,7 @@
         <v>42</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5338,7 +5356,7 @@
         <v>42</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5355,10 +5373,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5375,10 +5393,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E186" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5395,10 +5413,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>12</v>
+        <v>392</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5406,10 +5424,10 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
@@ -5418,7 +5436,7 @@
         <v>73</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5426,10 +5444,10 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
@@ -5438,7 +5456,7 @@
         <v>73</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5446,10 +5464,10 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
@@ -5458,7 +5476,7 @@
         <v>73</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5466,10 +5484,10 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
@@ -5478,7 +5496,7 @@
         <v>73</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5486,19 +5504,19 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>402</v>
+        <v>73</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5515,10 +5533,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>402</v>
+        <v>73</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5535,10 +5553,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>402</v>
+        <v>73</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5555,10 +5573,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5575,10 +5593,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5595,10 +5613,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5615,10 +5633,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5635,12 +5653,72 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="E199" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E202" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F199" s="1" t="s">
+      <c r="F202" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM01N.xlsx
+++ b/DJM01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="431">
   <si>
     <t/>
   </si>
@@ -148,297 +148,300 @@
     <t>ASPRO FLTR BOLD20'S</t>
   </si>
   <si>
+    <t>20138842</t>
+  </si>
+  <si>
+    <t>DUFF FILTER RED 20'S</t>
+  </si>
+  <si>
+    <t>20117725</t>
+  </si>
+  <si>
+    <t>NESLITE MAX 20'S</t>
+  </si>
+  <si>
+    <t>TG</t>
+  </si>
+  <si>
+    <t>20124230</t>
+  </si>
+  <si>
+    <t>MAGNUM MAX FILTER20S</t>
+  </si>
+  <si>
+    <t>10010094</t>
+  </si>
+  <si>
+    <t>SAMPOERNA KRT12S/PCS</t>
+  </si>
+  <si>
+    <t>20107794</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE EDS 12'S</t>
+  </si>
+  <si>
+    <t>10010088</t>
+  </si>
+  <si>
+    <t>234  KRT 12/PCS</t>
+  </si>
+  <si>
+    <t>20004283</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE MGNUM 12</t>
+  </si>
+  <si>
+    <t>20135213</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE KRT MGM</t>
+  </si>
+  <si>
+    <t>20138213</t>
+  </si>
+  <si>
+    <t>MAGNUM KRT CKLT 12'S</t>
+  </si>
+  <si>
+    <t>20134964</t>
+  </si>
+  <si>
+    <t>SMPOERNA LGT NIRA12S</t>
+  </si>
+  <si>
+    <t>20134790</t>
+  </si>
+  <si>
+    <t>SAMPOERNA PRIMA 12'S</t>
+  </si>
+  <si>
+    <t>20139534</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE S/P 12S</t>
+  </si>
+  <si>
+    <t>20139533</t>
+  </si>
+  <si>
+    <t>SMPOERNA PRMA SP 12S</t>
+  </si>
+  <si>
+    <t>20141927</t>
+  </si>
+  <si>
+    <t>MAGNUM 234 12S</t>
+  </si>
+  <si>
+    <t>20113074</t>
+  </si>
+  <si>
+    <t>MARLBORO KRETEK 12'S</t>
+  </si>
+  <si>
+    <t>20122038</t>
+  </si>
+  <si>
+    <t>MRLBORO KRT BIRU 12S</t>
+  </si>
+  <si>
+    <t>20126739</t>
+  </si>
+  <si>
+    <t>DUFF FILTER BOLD20'S</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20130572</t>
+  </si>
+  <si>
+    <t>BHUMI KRETEK 12S</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20043389</t>
+  </si>
+  <si>
+    <t>MARLBORO BLS/BRST 20</t>
+  </si>
+  <si>
+    <t>20107180</t>
+  </si>
+  <si>
+    <t>MRLBORO ICE BR SE20S</t>
+  </si>
+  <si>
+    <t>20135544</t>
+  </si>
+  <si>
+    <t>MARLBORO TRPCL BS16S</t>
+  </si>
+  <si>
+    <t>20070618</t>
+  </si>
+  <si>
+    <t>MARLBORO BLACK 20'S</t>
+  </si>
+  <si>
+    <t>20083490</t>
+  </si>
+  <si>
+    <t>MARLBORO BLACK 12'S</t>
+  </si>
+  <si>
+    <t>20105344</t>
+  </si>
+  <si>
+    <t>MARLBORO BLACK 16'S</t>
+  </si>
+  <si>
+    <t>20125676</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE MG BIN12</t>
+  </si>
+  <si>
+    <t>10030733</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE S/PRM</t>
+  </si>
+  <si>
+    <t>20134530</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE SP.PRM16</t>
+  </si>
+  <si>
+    <t>20132342</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE MAESTR12</t>
+  </si>
+  <si>
+    <t>20123283</t>
+  </si>
+  <si>
+    <t>TWIZZ R/F RYL CR 16S</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20123284</t>
+  </si>
+  <si>
+    <t>TWIZZ YELLOW CR 16'S</t>
+  </si>
+  <si>
+    <t>20129762</t>
+  </si>
+  <si>
+    <t>TWIZZ R/F RYL CR 12S</t>
+  </si>
+  <si>
+    <t>20139762</t>
+  </si>
+  <si>
+    <t>TWIZZ PRM ROYAL 16S</t>
+  </si>
+  <si>
+    <t>20139763</t>
+  </si>
+  <si>
+    <t>TWIZZ PRM TRPCL 16S</t>
+  </si>
+  <si>
+    <t>10010090</t>
+  </si>
+  <si>
+    <t>SAMPOERNA MLD 12/MRH</t>
+  </si>
+  <si>
+    <t>10010091</t>
+  </si>
+  <si>
+    <t>SAMPOERNA MILD 16'S</t>
+  </si>
+  <si>
+    <t>20135439</t>
+  </si>
+  <si>
+    <t>SAMPOERNA MLD CLS16S</t>
+  </si>
+  <si>
+    <t>20131370</t>
+  </si>
+  <si>
+    <t>SAMPOERNA ROYAL 16'S</t>
+  </si>
+  <si>
+    <t>20079512</t>
+  </si>
+  <si>
+    <t>SMPOERNA MNTHL.BR 16</t>
+  </si>
+  <si>
+    <t>20095217</t>
+  </si>
+  <si>
+    <t>SMPOERNA TRPCAL 16'S</t>
+  </si>
+  <si>
+    <t>20064088</t>
+  </si>
+  <si>
+    <t>SMPOERNA AVOLTN 20'S</t>
+  </si>
+  <si>
+    <t>20064089</t>
+  </si>
+  <si>
+    <t>SMPOERNA AVLT MNT 20</t>
+  </si>
+  <si>
+    <t>20138598</t>
+  </si>
+  <si>
+    <t>SMPOERN AVL RY.BRS20</t>
+  </si>
+  <si>
+    <t>10010100</t>
+  </si>
+  <si>
+    <t>MARLBORO HPACK 20'S</t>
+  </si>
+  <si>
+    <t>20107181</t>
+  </si>
+  <si>
+    <t>MARLBORO SE 20'S</t>
+  </si>
+  <si>
+    <t>10010102</t>
+  </si>
+  <si>
+    <t>MARLBORO LIGHT 20'S</t>
+  </si>
+  <si>
+    <t>20107184</t>
+  </si>
+  <si>
+    <t>MARLBORO GOLD SE 20S</t>
+  </si>
+  <si>
     <t>20137571</t>
   </si>
   <si>
     <t>TWIZZ PRIME 16'S</t>
   </si>
   <si>
-    <t>20123283</t>
-  </si>
-  <si>
-    <t>TWIZZ R/F RYL CR 16S</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20123284</t>
-  </si>
-  <si>
-    <t>TWIZZ YELLOW CR 16'S</t>
-  </si>
-  <si>
-    <t>20129762</t>
-  </si>
-  <si>
-    <t>TWIZZ R/F RYL CR 12S</t>
-  </si>
-  <si>
-    <t>20139762</t>
-  </si>
-  <si>
-    <t>TWIZZ PRM ROYAL 16S</t>
-  </si>
-  <si>
-    <t>20139763</t>
-  </si>
-  <si>
-    <t>TWIZZ PRM TRPCL 16S</t>
-  </si>
-  <si>
-    <t>20113074</t>
-  </si>
-  <si>
-    <t>MARLBORO KRETEK 12'S</t>
-  </si>
-  <si>
-    <t>20122038</t>
-  </si>
-  <si>
-    <t>MRLBORO KRT BIRU 12S</t>
-  </si>
-  <si>
-    <t>20126739</t>
-  </si>
-  <si>
-    <t>DUFF FILTER BOLD20'S</t>
-  </si>
-  <si>
-    <t>20130572</t>
-  </si>
-  <si>
-    <t>BHUMI KRETEK 12S</t>
-  </si>
-  <si>
-    <t>20138842</t>
-  </si>
-  <si>
-    <t>DUFF FILTER RED 20'S</t>
-  </si>
-  <si>
-    <t>20117725</t>
-  </si>
-  <si>
-    <t>NESLITE MAX 20'S</t>
-  </si>
-  <si>
-    <t>TG</t>
-  </si>
-  <si>
-    <t>20124230</t>
-  </si>
-  <si>
-    <t>MAGNUM MAX FILTER20S</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>10010094</t>
-  </si>
-  <si>
-    <t>SAMPOERNA KRT12S/PCS</t>
-  </si>
-  <si>
-    <t>20107794</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE EDS 12'S</t>
-  </si>
-  <si>
-    <t>10010088</t>
-  </si>
-  <si>
-    <t>234  KRT 12/PCS</t>
-  </si>
-  <si>
-    <t>20004283</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE MGNUM 12</t>
-  </si>
-  <si>
-    <t>20135213</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE KRT MGM</t>
-  </si>
-  <si>
-    <t>20138213</t>
-  </si>
-  <si>
-    <t>MAGNUM KRT CKLT 12'S</t>
-  </si>
-  <si>
-    <t>20134964</t>
-  </si>
-  <si>
-    <t>SMPOERNA LGT NIRA12S</t>
-  </si>
-  <si>
-    <t>20134790</t>
-  </si>
-  <si>
-    <t>SAMPOERNA PRIMA 12'S</t>
-  </si>
-  <si>
-    <t>20139534</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE S/P 12S</t>
-  </si>
-  <si>
-    <t>20132342</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE MAESTR12</t>
-  </si>
-  <si>
-    <t>20139533</t>
-  </si>
-  <si>
-    <t>SMPOERNA PRMA SP 12S</t>
-  </si>
-  <si>
-    <t>20141927</t>
-  </si>
-  <si>
-    <t>MAGNUM 234 12S</t>
-  </si>
-  <si>
-    <t>10010100</t>
-  </si>
-  <si>
-    <t>MARLBORO HPACK 20'S</t>
-  </si>
-  <si>
-    <t>20107181</t>
-  </si>
-  <si>
-    <t>MARLBORO SE 20'S</t>
-  </si>
-  <si>
-    <t>10010102</t>
-  </si>
-  <si>
-    <t>MARLBORO LIGHT 20'S</t>
-  </si>
-  <si>
-    <t>20107184</t>
-  </si>
-  <si>
-    <t>MARLBORO GOLD SE 20S</t>
-  </si>
-  <si>
-    <t>20043389</t>
-  </si>
-  <si>
-    <t>MARLBORO BLS/BRST 20</t>
-  </si>
-  <si>
-    <t>20107180</t>
-  </si>
-  <si>
-    <t>MRLBORO ICE BR SE20S</t>
-  </si>
-  <si>
-    <t>20135544</t>
-  </si>
-  <si>
-    <t>MARLBORO TRPCL BS16S</t>
-  </si>
-  <si>
-    <t>20070618</t>
-  </si>
-  <si>
-    <t>MARLBORO BLACK 20'S</t>
-  </si>
-  <si>
-    <t>20083490</t>
-  </si>
-  <si>
-    <t>MARLBORO BLACK 12'S</t>
-  </si>
-  <si>
-    <t>20105344</t>
-  </si>
-  <si>
-    <t>MARLBORO BLACK 16'S</t>
-  </si>
-  <si>
-    <t>20125676</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE MG BIN12</t>
-  </si>
-  <si>
-    <t>10030733</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE S/PRM</t>
-  </si>
-  <si>
-    <t>20134530</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE SP.PRM16</t>
-  </si>
-  <si>
-    <t>10010090</t>
-  </si>
-  <si>
-    <t>SAMPOERNA MLD 12/MRH</t>
-  </si>
-  <si>
-    <t>10010091</t>
-  </si>
-  <si>
-    <t>SAMPOERNA MILD 16'S</t>
-  </si>
-  <si>
-    <t>20135439</t>
-  </si>
-  <si>
-    <t>SAMPOERNA MLD CLS16S</t>
-  </si>
-  <si>
-    <t>20131370</t>
-  </si>
-  <si>
-    <t>SAMPOERNA ROYAL 16'S</t>
-  </si>
-  <si>
-    <t>20079512</t>
-  </si>
-  <si>
-    <t>SMPOERNA MNTHL.BR 16</t>
-  </si>
-  <si>
-    <t>20095217</t>
-  </si>
-  <si>
-    <t>SMPOERNA TRPCAL 16'S</t>
-  </si>
-  <si>
-    <t>20064088</t>
-  </si>
-  <si>
-    <t>SMPOERNA AVOLTN 20'S</t>
-  </si>
-  <si>
-    <t>20064089</t>
-  </si>
-  <si>
-    <t>SMPOERNA AVLT MNT 20</t>
-  </si>
-  <si>
-    <t>20138598</t>
-  </si>
-  <si>
-    <t>SMPOERN AVL RY.BRS20</t>
-  </si>
-  <si>
     <t>20033460</t>
   </si>
   <si>
@@ -649,6 +652,18 @@
     <t>DPLOMAT EVO MGO 16'S</t>
   </si>
   <si>
+    <t>20137798</t>
+  </si>
+  <si>
+    <t>DIPLOMAT EVO BERY16S</t>
+  </si>
+  <si>
+    <t>20139165</t>
+  </si>
+  <si>
+    <t>DIPLOMAT EVO LYCH16S</t>
+  </si>
+  <si>
     <t>20102167</t>
   </si>
   <si>
@@ -685,6 +700,18 @@
     <t>IDM LGHT CRCKT ELKTR</t>
   </si>
   <si>
+    <t>20142352</t>
+  </si>
+  <si>
+    <t>IDM UTILITY LIGHTER</t>
+  </si>
+  <si>
+    <t>20142409</t>
+  </si>
+  <si>
+    <t>IDM LIGHTER EL M2000</t>
+  </si>
+  <si>
     <t>20128084</t>
   </si>
   <si>
@@ -1187,9 +1214,6 @@
   </si>
   <si>
     <t>ESSE DOUBLE POP 16'S</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>20038143</t>
@@ -1672,7 +1696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F202"/>
+  <dimension ref="A1:F206"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2053,13 +2077,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2073,10 +2097,10 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -2093,13 +2117,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2113,10 +2137,10 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -2133,10 +2157,10 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -2153,13 +2177,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2173,10 +2197,10 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -2193,10 +2217,10 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2213,41 +2237,41 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -2256,18 +2280,18 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -2276,7 +2300,7 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2284,10 +2308,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -2296,18 +2320,18 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -2316,7 +2340,7 @@
         <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2324,10 +2348,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -2336,7 +2360,7 @@
         <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2353,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2373,10 +2397,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2393,10 +2417,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2413,13 +2437,13 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2433,10 +2457,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2453,10 +2477,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2473,13 +2497,13 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2496,10 +2520,10 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2516,7 +2540,7 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2536,7 +2560,7 @@
         <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2556,18 +2580,18 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2576,18 +2600,18 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2596,18 +2620,18 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2616,7 +2640,7 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2624,10 +2648,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2636,27 +2660,27 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2664,39 +2688,39 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2704,39 +2728,39 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2744,10 +2768,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2756,7 +2780,7 @@
         <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2764,10 +2788,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2776,18 +2800,18 @@
         <v>18</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2796,7 +2820,7 @@
         <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2804,10 +2828,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2816,18 +2840,18 @@
         <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2836,18 +2860,18 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2856,7 +2880,7 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2864,10 +2888,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2876,7 +2900,7 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2884,10 +2908,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2896,7 +2920,7 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2904,10 +2928,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2916,18 +2940,18 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2944,10 +2968,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2964,10 +2988,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2984,10 +3008,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -3004,10 +3028,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -3024,10 +3048,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -3044,10 +3068,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -3064,10 +3088,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -3084,10 +3108,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -3104,10 +3128,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -3124,10 +3148,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -3144,10 +3168,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -3164,10 +3188,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -3184,10 +3208,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -3204,10 +3228,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -3224,10 +3248,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -3244,10 +3268,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -3264,10 +3288,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -3284,10 +3308,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -3304,10 +3328,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -3324,10 +3348,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -3344,10 +3368,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -3356,7 +3380,7 @@
         <v>24</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3364,10 +3388,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3384,10 +3408,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3404,10 +3428,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3424,10 +3448,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3444,10 +3468,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3464,10 +3488,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3484,10 +3508,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3499,15 +3523,15 @@
         <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3524,10 +3548,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3544,10 +3568,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3564,10 +3588,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3584,10 +3608,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3604,10 +3628,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3624,10 +3648,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3644,10 +3668,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3656,7 +3680,7 @@
         <v>30</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3664,10 +3688,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3676,7 +3700,7 @@
         <v>30</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3684,10 +3708,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3704,10 +3728,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3719,15 +3743,15 @@
         <v>30</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3744,39 +3768,39 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3784,50 +3808,50 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3844,10 +3868,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3856,7 +3880,7 @@
         <v>33</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3864,10 +3888,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3876,7 +3900,7 @@
         <v>33</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3884,10 +3908,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3896,7 +3920,7 @@
         <v>33</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3904,10 +3928,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3916,7 +3940,7 @@
         <v>33</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3924,10 +3948,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3936,7 +3960,7 @@
         <v>33</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3944,10 +3968,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3956,7 +3980,7 @@
         <v>33</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3964,10 +3988,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3976,18 +4000,18 @@
         <v>33</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3996,7 +4020,7 @@
         <v>33</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4004,10 +4028,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -4016,7 +4040,7 @@
         <v>33</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -4024,10 +4048,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -4036,7 +4060,7 @@
         <v>33</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4044,10 +4068,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -4056,18 +4080,18 @@
         <v>33</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4079,15 +4103,15 @@
         <v>15</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4104,10 +4128,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4124,10 +4148,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -4136,7 +4160,7 @@
         <v>33</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4144,10 +4168,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4156,18 +4180,18 @@
         <v>33</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4176,7 +4200,7 @@
         <v>33</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4184,10 +4208,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4196,18 +4220,18 @@
         <v>33</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -4219,15 +4243,15 @@
         <v>18</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -4239,15 +4263,15 @@
         <v>18</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4264,10 +4288,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4279,15 +4303,15 @@
         <v>18</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4299,15 +4323,15 @@
         <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4319,15 +4343,15 @@
         <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4344,10 +4368,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4364,10 +4388,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4384,10 +4408,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4404,10 +4428,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4416,18 +4440,18 @@
         <v>33</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4436,18 +4460,18 @@
         <v>33</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -4456,18 +4480,18 @@
         <v>33</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
@@ -4476,18 +4500,18 @@
         <v>33</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
@@ -4499,15 +4523,15 @@
         <v>21</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
@@ -4519,15 +4543,15 @@
         <v>21</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
@@ -4539,15 +4563,15 @@
         <v>21</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
@@ -4559,15 +4583,15 @@
         <v>21</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
@@ -4584,10 +4608,10 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
@@ -4596,7 +4620,7 @@
         <v>33</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4604,19 +4628,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4624,19 +4648,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4644,19 +4668,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4664,19 +4688,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4684,10 +4708,10 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
@@ -4696,7 +4720,7 @@
         <v>36</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4704,10 +4728,10 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
@@ -4716,7 +4740,7 @@
         <v>36</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4724,10 +4748,10 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
@@ -4736,7 +4760,7 @@
         <v>36</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4744,10 +4768,10 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
@@ -4756,7 +4780,7 @@
         <v>36</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4764,10 +4788,10 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
@@ -4776,7 +4800,7 @@
         <v>36</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4784,10 +4808,10 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
@@ -4796,7 +4820,7 @@
         <v>36</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4804,10 +4828,10 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
@@ -4816,18 +4840,18 @@
         <v>36</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
@@ -4836,7 +4860,7 @@
         <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4844,10 +4868,10 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
@@ -4856,27 +4880,27 @@
         <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4884,39 +4908,39 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4924,30 +4948,30 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
@@ -4956,7 +4980,7 @@
         <v>39</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4964,10 +4988,10 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
@@ -4976,7 +5000,7 @@
         <v>39</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -4984,10 +5008,10 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
@@ -4996,7 +5020,7 @@
         <v>39</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5004,10 +5028,10 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
@@ -5016,7 +5040,7 @@
         <v>39</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5024,10 +5048,10 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
@@ -5036,7 +5060,7 @@
         <v>39</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5044,10 +5068,10 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
@@ -5056,7 +5080,7 @@
         <v>39</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5064,10 +5088,10 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
@@ -5076,7 +5100,7 @@
         <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5084,10 +5108,10 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
@@ -5096,7 +5120,7 @@
         <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5104,10 +5128,10 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
@@ -5116,7 +5140,7 @@
         <v>39</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5124,19 +5148,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5144,19 +5168,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5164,19 +5188,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5184,19 +5208,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E176" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5204,10 +5228,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
@@ -5216,7 +5240,7 @@
         <v>42</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5224,10 +5248,10 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
@@ -5236,18 +5260,18 @@
         <v>42</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
@@ -5256,18 +5280,18 @@
         <v>42</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
@@ -5276,18 +5300,18 @@
         <v>42</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
@@ -5296,7 +5320,7 @@
         <v>42</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5304,10 +5328,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
@@ -5316,18 +5340,18 @@
         <v>42</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
@@ -5336,18 +5360,18 @@
         <v>42</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
@@ -5356,18 +5380,18 @@
         <v>42</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
@@ -5376,7 +5400,7 @@
         <v>42</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5384,10 +5408,10 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
@@ -5396,7 +5420,7 @@
         <v>42</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5404,10 +5428,10 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
@@ -5416,7 +5440,7 @@
         <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>392</v>
+        <v>36</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5433,10 +5457,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5453,10 +5477,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5473,10 +5497,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5493,10 +5517,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5513,10 +5537,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5533,10 +5557,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5553,10 +5577,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5573,10 +5597,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>392</v>
+        <v>80</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5593,10 +5617,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>392</v>
+        <v>80</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5613,10 +5637,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>392</v>
+        <v>80</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5633,10 +5657,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>392</v>
+        <v>80</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5653,10 +5677,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5673,10 +5697,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5693,10 +5717,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5713,12 +5737,92 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="E202" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E206" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F202" s="1" t="s">
+      <c r="F206" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM01N.xlsx
+++ b/DJM01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="429">
   <si>
     <t/>
   </si>
@@ -896,12 +896,6 @@
   </si>
   <si>
     <t>VEEV ONE 1000 LT.TEA</t>
-  </si>
-  <si>
-    <t>20140266</t>
-  </si>
-  <si>
-    <t>VEEV ONE 500 LM.TEA</t>
   </si>
   <si>
     <t>20140267</t>
@@ -1696,7 +1690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F206"/>
+  <dimension ref="A1:F205"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4500,10 +4494,10 @@
         <v>33</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4583,7 +4577,7 @@
         <v>21</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4680,7 +4674,7 @@
         <v>33</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4697,10 +4691,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4720,7 +4714,7 @@
         <v>36</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4740,7 +4734,7 @@
         <v>36</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4760,7 +4754,7 @@
         <v>36</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4780,7 +4774,7 @@
         <v>36</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4800,7 +4794,7 @@
         <v>36</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4820,7 +4814,7 @@
         <v>36</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4840,7 +4834,7 @@
         <v>36</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4860,7 +4854,7 @@
         <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4880,7 +4874,7 @@
         <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4900,10 +4894,10 @@
         <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4920,10 +4914,10 @@
         <v>36</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4940,10 +4934,10 @@
         <v>36</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4957,13 +4951,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4980,7 +4974,7 @@
         <v>39</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5000,7 +4994,7 @@
         <v>39</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5020,7 +5014,7 @@
         <v>39</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5040,7 +5034,7 @@
         <v>39</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5060,7 +5054,7 @@
         <v>39</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5080,7 +5074,7 @@
         <v>39</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5100,7 +5094,7 @@
         <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5120,7 +5114,7 @@
         <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5140,7 +5134,7 @@
         <v>39</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5160,7 +5154,7 @@
         <v>39</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5180,7 +5174,7 @@
         <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5200,7 +5194,7 @@
         <v>39</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5217,10 +5211,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5240,7 +5234,7 @@
         <v>42</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5260,7 +5254,7 @@
         <v>42</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5280,7 +5274,7 @@
         <v>42</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5300,7 +5294,7 @@
         <v>42</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5320,10 +5314,10 @@
         <v>42</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5340,7 +5334,7 @@
         <v>42</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>9</v>
@@ -5360,7 +5354,7 @@
         <v>42</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>9</v>
@@ -5380,10 +5374,10 @@
         <v>42</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5400,7 +5394,7 @@
         <v>42</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5420,7 +5414,7 @@
         <v>42</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5440,7 +5434,7 @@
         <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5460,7 +5454,7 @@
         <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5480,7 +5474,7 @@
         <v>42</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5500,7 +5494,7 @@
         <v>42</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5517,10 +5511,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5540,7 +5534,7 @@
         <v>80</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5560,7 +5554,7 @@
         <v>80</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5580,7 +5574,7 @@
         <v>80</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5600,7 +5594,7 @@
         <v>80</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5620,7 +5614,7 @@
         <v>80</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5640,7 +5634,7 @@
         <v>80</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5657,10 +5651,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5680,7 +5674,7 @@
         <v>83</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5700,7 +5694,7 @@
         <v>83</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5720,7 +5714,7 @@
         <v>83</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5740,7 +5734,7 @@
         <v>83</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5760,7 +5754,7 @@
         <v>83</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5780,7 +5774,7 @@
         <v>83</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5800,29 +5794,9 @@
         <v>83</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F206" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM01N.xlsx
+++ b/DJM01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="433">
   <si>
     <t/>
   </si>
@@ -670,6 +670,12 @@
     <t>DIPLOMAT EVO16'S</t>
   </si>
   <si>
+    <t>20141244</t>
+  </si>
+  <si>
+    <t>WISMILAK SLIM LYC16S</t>
+  </si>
+  <si>
     <t>20101053</t>
   </si>
   <si>
@@ -902,6 +908,12 @@
   </si>
   <si>
     <t>VEEV ONE 1000 LM.TEA</t>
+  </si>
+  <si>
+    <t>20142476</t>
+  </si>
+  <si>
+    <t>VEEVA PODS GRAPE</t>
   </si>
   <si>
     <t>20137962</t>
@@ -1690,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F205"/>
+  <dimension ref="A1:F207"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3777,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3797,7 +3809,7 @@
         <v>39</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3817,7 +3829,7 @@
         <v>42</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3851,13 +3863,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3954,7 +3966,7 @@
         <v>33</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4014,7 +4026,7 @@
         <v>33</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4077,7 +4089,7 @@
         <v>12</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4094,10 +4106,10 @@
         <v>33</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4177,7 +4189,7 @@
         <v>15</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4197,7 +4209,7 @@
         <v>15</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4234,7 +4246,7 @@
         <v>33</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4297,7 +4309,7 @@
         <v>18</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4357,7 +4369,7 @@
         <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4494,10 +4506,10 @@
         <v>33</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4514,7 +4526,7 @@
         <v>33</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>9</v>
@@ -4577,7 +4589,7 @@
         <v>21</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4597,7 +4609,7 @@
         <v>21</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4674,7 +4686,7 @@
         <v>33</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4691,10 +4703,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4711,10 +4723,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4734,7 +4746,7 @@
         <v>36</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4754,7 +4766,7 @@
         <v>36</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4774,7 +4786,7 @@
         <v>36</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4794,7 +4806,7 @@
         <v>36</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4814,7 +4826,7 @@
         <v>36</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4834,7 +4846,7 @@
         <v>36</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4854,7 +4866,7 @@
         <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4874,7 +4886,7 @@
         <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4894,10 +4906,10 @@
         <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4914,7 +4926,7 @@
         <v>36</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4934,7 +4946,7 @@
         <v>36</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>9</v>
@@ -4951,10 +4963,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4971,13 +4983,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4994,7 +5006,7 @@
         <v>39</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5014,7 +5026,7 @@
         <v>39</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5034,7 +5046,7 @@
         <v>39</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5054,7 +5066,7 @@
         <v>39</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5074,7 +5086,7 @@
         <v>39</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5094,7 +5106,7 @@
         <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5114,7 +5126,7 @@
         <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5134,7 +5146,7 @@
         <v>39</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5154,7 +5166,7 @@
         <v>39</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5174,7 +5186,7 @@
         <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5194,7 +5206,7 @@
         <v>39</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5211,10 +5223,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5231,10 +5243,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E177" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5254,7 +5266,7 @@
         <v>42</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5274,7 +5286,7 @@
         <v>42</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5294,7 +5306,7 @@
         <v>42</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5314,10 +5326,10 @@
         <v>42</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5334,10 +5346,10 @@
         <v>42</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -5354,7 +5366,7 @@
         <v>42</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>9</v>
@@ -5374,10 +5386,10 @@
         <v>42</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5394,10 +5406,10 @@
         <v>42</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5414,7 +5426,7 @@
         <v>42</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5434,7 +5446,7 @@
         <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5454,7 +5466,7 @@
         <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5474,7 +5486,7 @@
         <v>42</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5494,7 +5506,7 @@
         <v>42</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5511,10 +5523,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5531,10 +5543,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5554,7 +5566,7 @@
         <v>80</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5574,7 +5586,7 @@
         <v>80</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5594,7 +5606,7 @@
         <v>80</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5614,7 +5626,7 @@
         <v>80</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5634,7 +5646,7 @@
         <v>80</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5651,10 +5663,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5671,10 +5683,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5694,7 +5706,7 @@
         <v>83</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5714,7 +5726,7 @@
         <v>83</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5734,7 +5746,7 @@
         <v>83</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5754,7 +5766,7 @@
         <v>83</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5774,7 +5786,7 @@
         <v>83</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5794,9 +5806,49 @@
         <v>83</v>
       </c>
       <c r="E205" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E207" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F205" s="1" t="s">
+      <c r="F207" s="1" t="s">
         <v>5</v>
       </c>
     </row>
